--- a/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
+++ b/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
@@ -1,21 +1,455 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/food-security-paper/output/tcac_food_table/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_E5FD3DC28F79A8D366075C52F37BD2729ACB5FED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA0893A-1CA8-406B-AEAF-9C449712FE1D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="141">
+  <si>
+    <t>articulo</t>
+  </si>
+  <si>
+    <t>subclase_ipc</t>
+  </si>
+  <si>
+    <t>subgrupos_gabas</t>
+  </si>
+  <si>
+    <t>parte_comestible_percent</t>
+  </si>
+  <si>
+    <t>energia_kcal</t>
+  </si>
+  <si>
+    <t>proteina_g</t>
+  </si>
+  <si>
+    <t>lipidos_g</t>
+  </si>
+  <si>
+    <t>carbohidratos_totales_g</t>
+  </si>
+  <si>
+    <t>calcio_mg</t>
+  </si>
+  <si>
+    <t>hierro_mg</t>
+  </si>
+  <si>
+    <t>zinc_mg</t>
+  </si>
+  <si>
+    <t>magnesio_mg</t>
+  </si>
+  <si>
+    <t>fosforo_mg</t>
+  </si>
+  <si>
+    <t>vitamina_c_mg</t>
+  </si>
+  <si>
+    <t>tiamina_mg</t>
+  </si>
+  <si>
+    <t>riboflavina_mg</t>
+  </si>
+  <si>
+    <t>niacina_mg</t>
+  </si>
+  <si>
+    <t>folatos_mcg</t>
+  </si>
+  <si>
+    <t>vitamina_b12_mcg</t>
+  </si>
+  <si>
+    <t>vitamina_a_er</t>
+  </si>
+  <si>
+    <t>sodio_mg</t>
+  </si>
+  <si>
+    <t>AZÚCAR NATURAL O MORENA</t>
+  </si>
+  <si>
+    <t>011801</t>
+  </si>
+  <si>
+    <t>AZUCARES SIMPLES</t>
+  </si>
+  <si>
+    <t>AZÚCAR REFINADA</t>
+  </si>
+  <si>
+    <t>PANELA</t>
+  </si>
+  <si>
+    <t>011802</t>
+  </si>
+  <si>
+    <t>CARNE DE CERDO SIN HUESO</t>
+  </si>
+  <si>
+    <t>011202</t>
+  </si>
+  <si>
+    <t>CARNES MAGRAS CRUDAS</t>
+  </si>
+  <si>
+    <t>PESCADO DE MAR</t>
+  </si>
+  <si>
+    <t>011303</t>
+  </si>
+  <si>
+    <t>PESCADO DE RÍO</t>
+  </si>
+  <si>
+    <t>PESCADO ENLATADO</t>
+  </si>
+  <si>
+    <t>VISCERAS - HIGADO</t>
+  </si>
+  <si>
+    <t>011201</t>
+  </si>
+  <si>
+    <t>HUEVOS</t>
+  </si>
+  <si>
+    <t>011405</t>
+  </si>
+  <si>
+    <t>ARVEJA SECA</t>
+  </si>
+  <si>
+    <t>011716</t>
+  </si>
+  <si>
+    <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
+  </si>
+  <si>
+    <t>FRÍJOL FRESCO</t>
+  </si>
+  <si>
+    <t>FRÍJOL SECO</t>
+  </si>
+  <si>
+    <t>FRÍJOL TARRO</t>
+  </si>
+  <si>
+    <t>011703</t>
+  </si>
+  <si>
+    <t>GARBANZO</t>
+  </si>
+  <si>
+    <t>011702</t>
+  </si>
+  <si>
+    <t>LENTEJAS</t>
+  </si>
+  <si>
+    <t>CARNE DE CERDO CON HUESO</t>
+  </si>
+  <si>
+    <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
+  </si>
+  <si>
+    <t>CARNE DE RES CON HUESO</t>
+  </si>
+  <si>
+    <t>CARNE DE RES SIN HUESO</t>
+  </si>
+  <si>
+    <t>POLLO DESPRESADO POR LIBRA</t>
+  </si>
+  <si>
+    <t>011203</t>
+  </si>
+  <si>
+    <t>POLLO ENTERO POR LIBRA</t>
+  </si>
+  <si>
+    <t>ARROZ PARA SECO</t>
+  </si>
+  <si>
+    <t>011101</t>
+  </si>
+  <si>
+    <t>CEREALES</t>
+  </si>
+  <si>
+    <t>ARROZ PARA SOPA</t>
+  </si>
+  <si>
+    <t>AVENA HOJUELAS</t>
+  </si>
+  <si>
+    <t>011103</t>
+  </si>
+  <si>
+    <t>AVENA MOLIDA</t>
+  </si>
+  <si>
+    <t>FECULA DE MAÍZ</t>
+  </si>
+  <si>
+    <t>011105</t>
+  </si>
+  <si>
+    <t>HARINA DE TRIGO</t>
+  </si>
+  <si>
+    <t>HARINA PRECOCIDA</t>
+  </si>
+  <si>
+    <t>011106</t>
+  </si>
+  <si>
+    <t>PAN CORRIENTE</t>
+  </si>
+  <si>
+    <t>011108</t>
+  </si>
+  <si>
+    <t>PAN FRANCÉS</t>
+  </si>
+  <si>
+    <t>PAN INTEGRAL</t>
+  </si>
+  <si>
+    <t>PASTA PARA SECO</t>
+  </si>
+  <si>
+    <t>011102</t>
+  </si>
+  <si>
+    <t>PASTA PARA SOPA</t>
+  </si>
+  <si>
+    <t>PLÁTANO</t>
+  </si>
+  <si>
+    <t>011704</t>
+  </si>
+  <si>
+    <t>PLÁTANOS</t>
+  </si>
+  <si>
+    <t>ARRACACHA</t>
+  </si>
+  <si>
+    <t>011712</t>
+  </si>
+  <si>
+    <t>RAÍCES</t>
+  </si>
+  <si>
+    <t>YUCA</t>
+  </si>
+  <si>
+    <t>011706</t>
+  </si>
+  <si>
+    <t>PAPA</t>
+  </si>
+  <si>
+    <t>011705</t>
+  </si>
+  <si>
+    <t>TUBÉRCULOS</t>
+  </si>
+  <si>
+    <t>PAPA CRIOLLA</t>
+  </si>
+  <si>
+    <t>BANANOS</t>
+  </si>
+  <si>
+    <t>011606</t>
+  </si>
+  <si>
+    <t>FRUTAS</t>
+  </si>
+  <si>
+    <t>CURUBAS</t>
+  </si>
+  <si>
+    <t>011609</t>
+  </si>
+  <si>
+    <t>GUAYABAS</t>
+  </si>
+  <si>
+    <t>LIMONES</t>
+  </si>
+  <si>
+    <t>LULOS</t>
+  </si>
+  <si>
+    <t>MANZANAS</t>
+  </si>
+  <si>
+    <t>MARACUYA</t>
+  </si>
+  <si>
+    <t>MORAS</t>
+  </si>
+  <si>
+    <t>011608</t>
+  </si>
+  <si>
+    <t>NARANJAS</t>
+  </si>
+  <si>
+    <t>011605</t>
+  </si>
+  <si>
+    <t>PAPAYAS</t>
+  </si>
+  <si>
+    <t>PIÑAS</t>
+  </si>
+  <si>
+    <t>TOMATE DE ÁRBOL</t>
+  </si>
+  <si>
+    <t>011607</t>
+  </si>
+  <si>
+    <t>AHUYAMA</t>
+  </si>
+  <si>
+    <t>VERDURAS</t>
+  </si>
+  <si>
+    <t>AJO</t>
+  </si>
+  <si>
+    <t>ARVEJA FRESCA</t>
+  </si>
+  <si>
+    <t>ARVEJA TARRO</t>
+  </si>
+  <si>
+    <t>CEBOLLA CABEZONA</t>
+  </si>
+  <si>
+    <t>011714</t>
+  </si>
+  <si>
+    <t>CEBOLLA LARGA</t>
+  </si>
+  <si>
+    <t>HABICHUELAS FRESCAS</t>
+  </si>
+  <si>
+    <t>LECHUGA</t>
+  </si>
+  <si>
+    <t>REPOLLO</t>
+  </si>
+  <si>
+    <t>TOMATE</t>
+  </si>
+  <si>
+    <t>011713</t>
+  </si>
+  <si>
+    <t>ZANAHORIA</t>
+  </si>
+  <si>
+    <t>011715</t>
+  </si>
+  <si>
+    <t>AGUACATE</t>
+  </si>
+  <si>
+    <t>GRASAS MONOINSATURADAS</t>
+  </si>
+  <si>
+    <t>MANTECA VEGETAL</t>
+  </si>
+  <si>
+    <t>011505</t>
+  </si>
+  <si>
+    <t>ACEITE DE GIRASOL</t>
+  </si>
+  <si>
+    <t>011501</t>
+  </si>
+  <si>
+    <t>GRASAS POLIINSATURADAS</t>
+  </si>
+  <si>
+    <t>ACEITE DE SOYA O DE MAÍZ</t>
+  </si>
+  <si>
+    <t>LECHE EN POLVO ENTERA</t>
+  </si>
+  <si>
+    <t>011401</t>
+  </si>
+  <si>
+    <t>LECHE ENTERA</t>
+  </si>
+  <si>
+    <t>LECHE EN POLVO LACTANTE</t>
+  </si>
+  <si>
+    <t>LECHE LARGA VIDA</t>
+  </si>
+  <si>
+    <t>LECHE PASTEURIZADA</t>
+  </si>
+  <si>
+    <t>QUESO CAMPESINO</t>
+  </si>
+  <si>
+    <t>011402</t>
+  </si>
+  <si>
+    <t>PRODUCTOS LACTEOS GRASA ENTERA</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>011902</t>
+  </si>
+  <si>
+    <t>SIN CATEGORIA</t>
+  </si>
+  <si>
+    <t>ARROZ INTEGRAL</t>
+  </si>
+  <si>
+    <t>CAMARONES O VARIEDAD DISPONIBLE</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +497,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +549,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +583,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +618,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,132 +794,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U73"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>articulo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>subclase_ipc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>subgrupos_gabas</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>parte_comestible_percent</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>energia_kcal</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>proteina_g</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lipidos_g</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>carbohidratos_totales_g</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>calcio_mg</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>hierro_mg</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>zinc_mg</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>magnesio_mg</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fosforo_mg</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>vitamina_c_mg</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>tiamina_mg</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>riboflavina_mg</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>niacina_mg</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>folatos_mcg</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>vitamina_b12_mcg</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>vitamina_a_er</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sodio_mg</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AZÚCAR NATURAL O MORENA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>011801</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AZUCARES SIMPLES</t>
-        </is>
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -532,21 +933,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AZÚCAR REFINADA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>011801</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AZUCARES SIMPLES</t>
-        </is>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -603,21 +998,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PANELA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>011802</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AZUCARES SIMPLES</t>
-        </is>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -638,7 +1027,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="K4">
         <v>1.4</v>
@@ -674,21 +1063,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CARNE DE CERDO SIN HUESO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>011202</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CARNES MAGRAS CRUDAS</t>
-        </is>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -745,21 +1128,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PESCADO DE MAR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>011303</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CARNES MAGRAS CRUDAS</t>
-        </is>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
       </c>
       <c r="D6">
         <v>62</v>
@@ -768,7 +1145,7 @@
         <v>96</v>
       </c>
       <c r="F6">
-        <v>20.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="G6">
         <v>1.7</v>
@@ -816,21 +1193,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PESCADO DE RÍO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>011303</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CARNES MAGRAS CRUDAS</t>
-        </is>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
       </c>
       <c r="D7">
         <v>64</v>
@@ -887,21 +1258,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PESCADO ENLATADO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>011303</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CARNES MAGRAS CRUDAS</t>
-        </is>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -949,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -958,21 +1323,15 @@
         <v>391</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VISCERAS - HIGADO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>011201</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CARNES MAGRAS CRUDAS</t>
-        </is>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -981,7 +1340,7 @@
         <v>138</v>
       </c>
       <c r="F9">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="G9">
         <v>4.5</v>
@@ -1029,21 +1388,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>HUEVOS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>011405</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HUEVOS</t>
-        </is>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
       </c>
       <c r="D10">
         <v>90</v>
@@ -1079,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P10">
         <v>0.49</v>
@@ -1100,21 +1453,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ARVEJA SECA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -1126,7 +1473,7 @@
         <v>23.9</v>
       </c>
       <c r="G11">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H11">
         <v>60.2</v>
@@ -1135,7 +1482,7 @@
         <v>60</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="K11">
         <v>3.5</v>
@@ -1171,21 +1518,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FRÍJOL FRESCO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
       </c>
       <c r="D12">
         <v>50</v>
@@ -1242,21 +1583,15 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FRÍJOL SECO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -1313,21 +1648,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FRÍJOL TARRO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>011703</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -1384,21 +1713,15 @@
         <v>218.65</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GARBANZO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>011702</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -1407,7 +1730,7 @@
         <v>393</v>
       </c>
       <c r="F15">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G15">
         <v>5.5</v>
@@ -1455,21 +1778,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LENTEJAS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>011702</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LEGUMINOSAS COCIDAS Y MEZCLAS VEGETALES COCIDAS</t>
-        </is>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
       </c>
       <c r="D16">
         <v>100</v>
@@ -1526,21 +1843,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CARNE DE CERDO CON HUESO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>011202</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
-        </is>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
       </c>
       <c r="D17">
         <v>77</v>
@@ -1582,7 +1893,7 @@
         <v>0.26</v>
       </c>
       <c r="Q17">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="R17">
         <v>4</v>
@@ -1597,21 +1908,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CARNE DE RES CON HUESO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>011201</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
-        </is>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
       </c>
       <c r="D18">
         <v>73</v>
@@ -1620,13 +1925,13 @@
         <v>287</v>
       </c>
       <c r="F18">
-        <v>17.1</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="G18">
         <v>23.3</v>
       </c>
       <c r="H18">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -1653,7 +1958,7 @@
         <v>0.18</v>
       </c>
       <c r="Q18">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="R18">
         <v>5</v>
@@ -1668,21 +1973,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CARNE DE RES SIN HUESO</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>011201</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
-        </is>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
       </c>
       <c r="D19">
         <v>100</v>
@@ -1739,21 +2038,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>POLLO DESPRESADO POR LIBRA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>011203</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
-        </is>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
       </c>
       <c r="D20">
         <v>93</v>
@@ -1765,7 +2058,7 @@
         <v>20.7</v>
       </c>
       <c r="G20">
-        <v>9.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H20">
         <v>0.1</v>
@@ -1789,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P20">
         <v>0.09</v>
@@ -1810,21 +2103,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>POLLO ENTERO POR LIBRA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>011203</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PRODUCTOS ALTOS EN GRASAS SATURADAS Y COLESTEROL</t>
-        </is>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -1833,7 +2120,7 @@
         <v>167</v>
       </c>
       <c r="F21">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="G21">
         <v>10.3</v>
@@ -1881,21 +2168,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ARROZ PARA SECO</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>011101</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -1910,7 +2191,7 @@
         <v>0.4</v>
       </c>
       <c r="H22">
-        <v>80.09999999999999</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -1931,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P22">
         <v>0.03</v>
@@ -1952,21 +2233,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ARROZ PARA SOPA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>011101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -1981,7 +2256,7 @@
         <v>0.4</v>
       </c>
       <c r="H23">
-        <v>80.09999999999999</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2002,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P23">
         <v>0.03</v>
@@ -2023,21 +2298,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AVENA HOJUELAS</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>011103</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
       </c>
       <c r="D24">
         <v>100</v>
@@ -2046,13 +2315,13 @@
         <v>411</v>
       </c>
       <c r="F24">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="G24">
         <v>7.5</v>
       </c>
       <c r="H24">
-        <v>64.09999999999999</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="I24">
         <v>54</v>
@@ -2094,21 +2363,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AVENA MOLIDA</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>011103</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" t="s">
+        <v>57</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -2165,21 +2428,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FECULA DE MAÍZ</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>011105</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -2194,7 +2451,7 @@
         <v>0.1</v>
       </c>
       <c r="H26">
-        <v>91.40000000000001</v>
+        <v>91.4</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -2236,21 +2493,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>HARINA DE TRIGO</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>011105</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
       </c>
       <c r="D27">
         <v>100</v>
@@ -2307,21 +2558,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HARINA PRECOCIDA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>011106</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -2336,7 +2581,7 @@
         <v>3.7</v>
       </c>
       <c r="H28">
-        <v>73.90000000000001</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="I28">
         <v>4</v>
@@ -2378,21 +2623,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PAN CORRIENTE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>011108</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -2431,7 +2670,7 @@
         <v>0.46</v>
       </c>
       <c r="P29">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q29">
         <v>3.6</v>
@@ -2449,21 +2688,15 @@
         <v>541</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PAN FRANCÉS</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>011108</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
       </c>
       <c r="D30">
         <v>100</v>
@@ -2520,21 +2753,15 @@
         <v>625</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PAN INTEGRAL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>011108</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -2591,21 +2818,15 @@
         <v>448</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PASTA PARA SECO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>011102</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -2662,21 +2883,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PASTA PARA SOPA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>011102</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CEREALES</t>
-        </is>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -2733,21 +2948,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PLÁTANO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>011704</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PLÁTANOS</t>
-        </is>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
       </c>
       <c r="D34">
         <v>65</v>
@@ -2756,7 +2965,7 @@
         <v>136</v>
       </c>
       <c r="F34">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G34">
         <v>0.3</v>
@@ -2804,21 +3013,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ARRACACHA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>011712</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>RAÍCES</t>
-        </is>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
       </c>
       <c r="D35">
         <v>80</v>
@@ -2875,21 +3078,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>YUCA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>011706</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>RAÍCES</t>
-        </is>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
       </c>
       <c r="D36">
         <v>80</v>
@@ -2946,21 +3143,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PAPA</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>011705</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>TUBÉRCULOS</t>
-        </is>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -2975,7 +3166,7 @@
         <v>0.1</v>
       </c>
       <c r="H37">
-        <v>18.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="I37">
         <v>12</v>
@@ -3002,7 +3193,7 @@
         <v>0.03</v>
       </c>
       <c r="Q37">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R37">
         <v>16</v>
@@ -3017,21 +3208,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PAPA CRIOLLA</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>011705</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TUBÉRCULOS</t>
-        </is>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -3040,7 +3225,7 @@
         <v>96</v>
       </c>
       <c r="F38">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G38">
         <v>0.1</v>
@@ -3055,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="K38">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L38">
         <v>23</v>
@@ -3088,21 +3273,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BANANOS</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>011606</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
       </c>
       <c r="D39">
         <v>70</v>
@@ -3159,21 +3338,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CURUBAS</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
       </c>
       <c r="D40">
         <v>50</v>
@@ -3230,21 +3403,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>GUAYABAS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
       </c>
       <c r="D41">
         <v>75</v>
@@ -3301,21 +3468,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LIMONES</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" t="s">
+        <v>88</v>
       </c>
       <c r="D42">
         <v>50</v>
@@ -3330,7 +3491,7 @@
         <v>0.3</v>
       </c>
       <c r="H42">
-        <v>9.300000000000001</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I42">
         <v>19</v>
@@ -3372,21 +3533,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LULOS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
       </c>
       <c r="D43">
         <v>60</v>
@@ -3443,21 +3598,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MANZANAS</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" t="s">
+        <v>88</v>
       </c>
       <c r="D44">
         <v>85</v>
@@ -3514,21 +3663,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MARACUYA</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" t="s">
+        <v>88</v>
       </c>
       <c r="D45">
         <v>32</v>
@@ -3585,21 +3728,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MORAS</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>011608</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
       </c>
       <c r="D46">
         <v>90</v>
@@ -3656,21 +3793,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NARANJAS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>011605</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
       </c>
       <c r="D47">
         <v>60</v>
@@ -3685,7 +3816,7 @@
         <v>0.3</v>
       </c>
       <c r="H47">
-        <v>8.800000000000001</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="I47">
         <v>33</v>
@@ -3727,21 +3858,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>PAPAYAS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" t="s">
+        <v>88</v>
       </c>
       <c r="D48">
         <v>70</v>
@@ -3756,7 +3881,7 @@
         <v>0.1</v>
       </c>
       <c r="H48">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="I48">
         <v>24</v>
@@ -3798,21 +3923,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>PIÑAS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" t="s">
+        <v>88</v>
       </c>
       <c r="D49">
         <v>55</v>
@@ -3869,21 +3988,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>TOMATE DE ÁRBOL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>011607</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FRUTAS</t>
-        </is>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
       </c>
       <c r="D50">
         <v>86</v>
@@ -3898,7 +4011,7 @@
         <v>0.2</v>
       </c>
       <c r="H50">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="I50">
         <v>10</v>
@@ -3925,7 +4038,7 @@
         <v>0.03</v>
       </c>
       <c r="Q50">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R50">
         <v>7</v>
@@ -3940,21 +4053,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>AHUYAMA</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>105</v>
       </c>
       <c r="D51">
         <v>85</v>
@@ -4011,21 +4118,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AJO</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>105</v>
       </c>
       <c r="D52">
         <v>95</v>
@@ -4064,7 +4165,7 @@
         <v>0.12</v>
       </c>
       <c r="P52">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q52">
         <v>0.7</v>
@@ -4082,21 +4183,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ARVEJA FRESCA</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>105</v>
       </c>
       <c r="D53">
         <v>40</v>
@@ -4138,7 +4233,7 @@
         <v>0.12</v>
       </c>
       <c r="Q53">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="R53">
         <v>65</v>
@@ -4153,21 +4248,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ARVEJA TARRO</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>011703</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" t="s">
+        <v>105</v>
       </c>
       <c r="D54">
         <v>100</v>
@@ -4176,7 +4265,7 @@
         <v>126.76</v>
       </c>
       <c r="F54">
-        <v>8.449999999999999</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="G54">
         <v>0.7</v>
@@ -4200,7 +4289,7 @@
         <v>67</v>
       </c>
       <c r="N54">
-        <v>8.529999999999999</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="O54">
         <v>0.1</v>
@@ -4224,21 +4313,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CEBOLLA CABEZONA</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>011714</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" t="s">
+        <v>105</v>
       </c>
       <c r="D55">
         <v>95</v>
@@ -4295,21 +4378,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>CEBOLLA LARGA</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>011714</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" t="s">
+        <v>105</v>
       </c>
       <c r="D56">
         <v>40</v>
@@ -4366,21 +4443,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>HABICHUELAS FRESCAS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>105</v>
       </c>
       <c r="D57">
         <v>90</v>
@@ -4437,21 +4508,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LECHUGA</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
       </c>
       <c r="D58">
         <v>55</v>
@@ -4508,21 +4573,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>REPOLLO</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>011716</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" t="s">
+        <v>105</v>
       </c>
       <c r="D59">
         <v>70</v>
@@ -4579,21 +4638,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TOMATE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>011713</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" t="s">
+        <v>105</v>
       </c>
       <c r="D60">
         <v>80</v>
@@ -4608,7 +4661,7 @@
         <v>0.1</v>
       </c>
       <c r="H60">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I60">
         <v>9</v>
@@ -4650,21 +4703,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ZANAHORIA</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>011715</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>VERDURAS</t>
-        </is>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
       </c>
       <c r="D61">
         <v>85</v>
@@ -4721,21 +4768,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>AGUACATE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>011609</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>GRASAS MONOINSATURADAS</t>
-        </is>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
+        <v>120</v>
       </c>
       <c r="D62">
         <v>77</v>
@@ -4792,21 +4833,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MANTECA VEGETAL</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>011505</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>GRASAS MONOINSATURADAS</t>
-        </is>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" t="s">
+        <v>120</v>
       </c>
       <c r="D63">
         <v>100</v>
@@ -4818,7 +4853,7 @@
         <v>0.6</v>
       </c>
       <c r="G63">
-        <v>81.09999999999999</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -4863,21 +4898,15 @@
         <v>877</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ACEITE DE GIRASOL</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>011501</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>GRASAS POLIINSATURADAS</t>
-        </is>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" t="s">
+        <v>125</v>
       </c>
       <c r="D64">
         <v>100</v>
@@ -4934,21 +4963,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ACEITE DE SOYA O DE MAÍZ</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>011501</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>GRASAS POLIINSATURADAS</t>
-        </is>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" t="s">
+        <v>124</v>
+      </c>
+      <c r="C65" t="s">
+        <v>125</v>
       </c>
       <c r="D65">
         <v>100</v>
@@ -5005,21 +5028,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>LECHE EN POLVO ENTERA</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>011401</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>LECHE ENTERA</t>
-        </is>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" t="s">
+        <v>129</v>
       </c>
       <c r="D66">
         <v>100</v>
@@ -5076,21 +5093,15 @@
         <v>369</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>LECHE EN POLVO LACTANTE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>011401</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>LECHE ENTERA</t>
-        </is>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" t="s">
+        <v>129</v>
       </c>
       <c r="D67">
         <v>100</v>
@@ -5147,21 +5158,15 @@
         <v>369</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>LECHE LARGA VIDA</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>011401</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>LECHE ENTERA</t>
-        </is>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" t="s">
+        <v>129</v>
       </c>
       <c r="D68">
         <v>100</v>
@@ -5218,21 +5223,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>LECHE PASTEURIZADA</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>011401</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>LECHE ENTERA</t>
-        </is>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" t="s">
+        <v>129</v>
       </c>
       <c r="D69">
         <v>100</v>
@@ -5289,21 +5288,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>QUESO CAMPESINO</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>011402</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>PRODUCTOS LACTEOS GRASA ENTERA</t>
-        </is>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" t="s">
+        <v>135</v>
       </c>
       <c r="D70">
         <v>100</v>
@@ -5360,21 +5353,15 @@
         <v>935</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>SAL</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>011902</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SIN CATEGORIA</t>
-        </is>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" t="s">
+        <v>137</v>
+      </c>
+      <c r="C71" t="s">
+        <v>138</v>
       </c>
       <c r="D71">
         <v>100</v>
@@ -5431,28 +5418,20 @@
         <v>38781</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>ARROZ INTEGRAL</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>011101</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CAMARONES O VARIEDAD DISPONIBLE</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>011303</t>
-        </is>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
+++ b/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/food-security-paper/output/tcac_food_table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_E5FD3DC28F79A8D366075C52F37BD2729ACB5FED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BA0893A-1CA8-406B-AEAF-9C449712FE1D}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_E5FD3DC28F79A8D366075C52F37BD2729ACB5FED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2FC2BC1-B56F-4513-8B25-A37A65231538}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,6 +799,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
   </cols>

--- a/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
+++ b/Proyecto Interno/food-security-paper/output/tcac_food_table/appendix_S1_food_items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/food-security-paper/output/tcac_food_table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_E5FD3DC28F79A8D366075C52F37BD2729ACB5FED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2FC2BC1-B56F-4513-8B25-A37A65231538}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_5C861EC88F79A8D366075C52F37BD272FA45299B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA0CAD8-7F27-44C1-BDC4-0A9DE7EAEA51}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -798,10 +798,8 @@
   <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4299,7 +4297,7 @@
         <v>0.08</v>
       </c>
       <c r="Q54">
-        <v>1815</v>
+        <v>1.81</v>
       </c>
       <c r="R54">
         <v>63</v>
